--- a/rules/CORE-001043/negative/01/data/unit-test-coreid-FB0501-negative.xlsx
+++ b/rules/CORE-001043/negative/01/data/unit-test-coreid-FB0501-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-001043\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFFD16-6FB6-4CF9-807E-83439632A17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEAF13E-D406-409A-B8F7-7BD10BFBAED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>Product</t>
   </si>
@@ -290,9 +290,6 @@
   </si>
   <si>
     <t>CDISC007</t>
-  </si>
-  <si>
-    <t>CDISC008</t>
   </si>
   <si>
     <t>CDISC009</t>
@@ -417,7 +414,7 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -780,7 +777,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -811,7 +808,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="12">
         <v>5</v>
@@ -829,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="12">
         <v>5</v>
@@ -849,7 +846,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="12">
         <v>5</v>
@@ -859,7 +856,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -867,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="12">
         <v>6</v>
@@ -875,7 +872,9 @@
       <c r="E5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="12">
@@ -885,7 +884,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="12">
         <v>6</v>
@@ -893,9 +892,7 @@
       <c r="E6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>79</v>
-      </c>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="12">
@@ -905,7 +902,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="12">
         <v>6</v>
@@ -915,61 +912,21 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A8" s="12">
-        <v>3</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="12">
-        <v>7</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>91</v>
-      </c>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="12">
-        <v>3</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="12">
-        <v>7</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="12">
-        <v>3</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="12">
-        <v>7</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -978,7 +935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:26" ht="29.15" x14ac:dyDescent="0.4">
@@ -1386,7 +1343,7 @@
         <v>89</v>
       </c>
       <c r="D6" s="8">
-        <v>1402</v>
+        <v>1502</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>82</v>
@@ -1425,83 +1382,15 @@
       <c r="S6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="T6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="W6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="X6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="10" t="s">
+        <v>90</v>
+      </c>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1502</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" s="8">
-        <v>701</v>
-      </c>
-      <c r="N7" s="9">
-        <v>1933</v>
-      </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7" t="s">
         <v>87</v>
       </c>
     </row>
